--- a/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/关卡_关卡运作表_Level_LevelOperationConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/关卡_关卡运作表_Level_LevelOperationConfig.xlsx
@@ -1,295 +1,177 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Work\Cursor\Gravedigger2026\Gravedigger2026\Gravedigger2026\Assets\ConfigTables\Mode2\Excel\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27945" windowHeight="12255" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="30">
-  <si>
-    <t>关卡ID</t>
-  </si>
-  <si>
-    <t>阶段编号</t>
-  </si>
-  <si>
-    <t>玩法类型</t>
-  </si>
-  <si>
-    <t>玩法配置ID</t>
-  </si>
-  <si>
-    <t>同 ID 多行 = 该关全部阶段</t>
-  </si>
-  <si>
-    <t>同关卡内升序执行；建议同关卡内唯一</t>
-  </si>
-  <si>
-    <t>如 Dig / AutoManufacture / UpgradeManufacture / Defend / PushMap</t>
-  </si>
-  <si>
-    <t>Dig→DigGameplayConfig；Defend→RecommendedConfigId；PushMap→PushMapGameplayConfig；UM/AutoManufacture→忽略</t>
-  </si>
-  <si>
-    <t>LevelId</t>
-  </si>
-  <si>
-    <t>StageNumber</t>
-  </si>
-  <si>
-    <t>GameplayType</t>
-  </si>
-  <si>
-    <t>GameplayConfigId</t>
-  </si>
-  <si>
-    <t>Level_01</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>Dig</t>
-  </si>
-  <si>
-    <t>Dig_01</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>AutoManufacture</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>UpgradeManufacture</t>
-  </si>
-  <si>
-    <t>PushMap_01</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>PushMap</t>
-  </si>
-  <si>
-    <t>Level_02</t>
-  </si>
-  <si>
-    <t>Dig_02</t>
-  </si>
-  <si>
-    <t>PushMap_02</t>
-  </si>
-  <si>
-    <t>Level_03</t>
-  </si>
-  <si>
-    <t>Dig_03</t>
-  </si>
-  <si>
-    <t>PushMap_03</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="20">
     <font>
-      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="34">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -596,154 +478,154 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -797,11 +679,74 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1088,227 +1033,391 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:D15"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D18"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="3" max="3" width="19.625" customWidth="1"/>
-    <col min="4" max="4" width="19.375" customWidth="1"/>
+    <col width="19.625" customWidth="1" min="3" max="3"/>
+    <col width="19.375" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" spans="1:4">
-      <c r="A3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" t="s">
-        <v>24</v>
-      </c>
-      <c r="B8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" t="s">
-        <v>14</v>
-      </c>
-      <c r="D8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" t="s">
-        <v>24</v>
-      </c>
-      <c r="B9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" t="s">
-        <v>17</v>
-      </c>
-      <c r="D9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" t="s">
-        <v>24</v>
-      </c>
-      <c r="B10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C10" t="s">
-        <v>20</v>
-      </c>
-      <c r="D10" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" t="s">
-        <v>24</v>
-      </c>
-      <c r="B11" t="s">
-        <v>22</v>
-      </c>
-      <c r="C11" t="s">
-        <v>23</v>
-      </c>
-      <c r="D11" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" t="s">
-        <v>27</v>
-      </c>
-      <c r="B12" t="s">
-        <v>13</v>
-      </c>
-      <c r="C12" t="s">
-        <v>14</v>
-      </c>
-      <c r="D12" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" t="s">
-        <v>27</v>
-      </c>
-      <c r="B13" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" t="s">
-        <v>17</v>
-      </c>
-      <c r="D13" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" t="s">
-        <v>27</v>
-      </c>
-      <c r="B14" t="s">
-        <v>19</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" t="s">
-        <v>27</v>
-      </c>
-      <c r="B15" t="s">
-        <v>22</v>
-      </c>
-      <c r="C15" t="s">
-        <v>23</v>
-      </c>
-      <c r="D15" t="s">
-        <v>29</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>关卡ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>阶段编号</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>玩法类型</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>玩法配置ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>同 ID 多行 = 该关全部阶段</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>同关卡内升序执行；建议同关卡内唯一</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>如 Shop / Dig / AutoManufacture / UpgradeManufacture / Defend / PushMap</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Dig→DigGameplayConfig；Defend→RecommendedConfigId；PushMap→PushMapGameplayConfig；Shop/UM/AutoManufacture→忽略</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" customFormat="1" s="1">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>LevelId</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>StageNumber</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>GameplayType</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>GameplayConfigId</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Level_01</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Shop</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Level_01</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Dig</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Dig_01</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Level_01</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>AutoManufacture</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Level_01</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>UpgradeManufacture</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>PushMap_01</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Level_01</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>PushMap</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>PushMap_01</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Level_02</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Shop</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Level_02</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Dig</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Dig_02</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Level_02</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>AutoManufacture</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Level_02</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>UpgradeManufacture</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>PushMap_02</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Level_02</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>PushMap</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>PushMap_02</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Level_03</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Shop</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Level_03</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Dig</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Dig_03</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Level_03</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>AutoManufacture</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Level_03</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>UpgradeManufacture</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>PushMap_03</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Level_03</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>PushMap</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>PushMap_03</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/关卡_关卡运作表_Level_LevelOperationConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/关卡_关卡运作表_Level_LevelOperationConfig.xlsx
@@ -515,12 +515,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="37">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -863,7 +869,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
@@ -887,16 +893,16 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="6">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="6">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
@@ -905,89 +911,89 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="34" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="35" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="36" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="36" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="37" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -996,6 +1002,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1418,10 +1425,10 @@
       <c r="A3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -1445,7 +1452,7 @@
       <c r="J3" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="K3" t="s">
+      <c r="K3" s="3" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1462,7 +1469,7 @@
       <c r="D4" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="4" t="s">
         <v>34</v>
       </c>
       <c r="J4" t="s">
@@ -1482,10 +1489,10 @@
       <c r="D5" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="4" t="s">
         <v>38</v>
       </c>
       <c r="J5" t="s">
@@ -1505,7 +1512,7 @@
       <c r="D6" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="4" t="s">
         <v>40</v>
       </c>
       <c r="J6" t="s">
@@ -1525,7 +1532,7 @@
       <c r="D7" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="4" t="s">
         <v>42</v>
       </c>
       <c r="J7" t="s">
@@ -1545,13 +1552,13 @@
       <c r="D8" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="E8" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="F8" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="G8" s="4" t="s">
         <v>46</v>
       </c>
       <c r="J8" t="s">
@@ -1571,13 +1578,13 @@
       <c r="D9" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="F9" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="G9" s="4" t="s">
         <v>50</v>
       </c>
       <c r="J9" t="s">
@@ -1597,10 +1604,10 @@
       <c r="D10" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="E10" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="F10" s="4" t="s">
         <v>53</v>
       </c>
       <c r="J10" t="s">
@@ -1620,10 +1627,10 @@
       <c r="D11" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="E11" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="F11" s="4" t="s">
         <v>56</v>
       </c>
       <c r="J11" t="s">
@@ -1643,10 +1650,10 @@
       <c r="D12" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="E12" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="F12" s="3" t="s">
+      <c r="F12" s="4" t="s">
         <v>59</v>
       </c>
       <c r="J12" t="s">
@@ -1666,7 +1673,7 @@
       <c r="D13" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="E13" s="4" t="s">
         <v>61</v>
       </c>
       <c r="J13" t="s">
@@ -1686,7 +1693,7 @@
       <c r="D14" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="E14" s="4" t="s">
         <v>63</v>
       </c>
       <c r="J14" t="s">
@@ -1706,13 +1713,13 @@
       <c r="D15" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="E15" s="5" t="s">
         <v>66</v>
       </c>
       <c r="J15" t="s">
         <v>35</v>
       </c>
-      <c r="K15" s="3" t="s">
+      <c r="K15" s="4" t="s">
         <v>63</v>
       </c>
     </row>
@@ -1729,10 +1736,10 @@
       <c r="D16" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E16" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="F16" s="5" t="s">
         <v>68</v>
       </c>
       <c r="J16" t="s">
@@ -1752,7 +1759,7 @@
       <c r="D17" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="E17" s="5" t="s">
         <v>69</v>
       </c>
       <c r="J17" t="s">
@@ -1772,7 +1779,7 @@
       <c r="D18" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E18" s="4" t="s">
+      <c r="E18" s="5" t="s">
         <v>70</v>
       </c>
       <c r="J18" t="s">
@@ -1792,13 +1799,13 @@
       <c r="D19" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E19" s="4" t="s">
+      <c r="E19" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="F19" s="4" t="s">
+      <c r="F19" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="G19" s="4" t="s">
+      <c r="G19" s="5" t="s">
         <v>73</v>
       </c>
       <c r="J19" t="s">
@@ -1818,13 +1825,13 @@
       <c r="D20" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="E20" s="4" t="s">
+      <c r="E20" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="F20" s="4" t="s">
+      <c r="F20" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="G20" s="4" t="s">
+      <c r="G20" s="5" t="s">
         <v>76</v>
       </c>
       <c r="J20" t="s">
@@ -1844,10 +1851,10 @@
       <c r="D21" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="E21" s="4" t="s">
+      <c r="E21" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="F21" s="4" t="s">
+      <c r="F21" s="5" t="s">
         <v>78</v>
       </c>
       <c r="J21" t="s">
@@ -1867,10 +1874,10 @@
       <c r="D22" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="E22" s="4" t="s">
+      <c r="E22" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="F22" s="4" t="s">
+      <c r="F22" s="5" t="s">
         <v>80</v>
       </c>
       <c r="J22" t="s">
@@ -1890,10 +1897,10 @@
       <c r="D23" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E23" s="4" t="s">
+      <c r="E23" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="F23" s="4" t="s">
+      <c r="F23" s="5" t="s">
         <v>82</v>
       </c>
       <c r="J23" t="s">
@@ -1913,7 +1920,7 @@
       <c r="D24" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E24" s="4" t="s">
+      <c r="E24" s="5" t="s">
         <v>83</v>
       </c>
       <c r="J24" t="s">
@@ -1933,7 +1940,7 @@
       <c r="D25" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="E25" s="4" t="s">
+      <c r="E25" s="5" t="s">
         <v>84</v>
       </c>
       <c r="J25" t="s">
@@ -1953,13 +1960,13 @@
       <c r="D26" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E26" s="5" t="s">
+      <c r="E26" s="6" t="s">
         <v>87</v>
       </c>
       <c r="J26" t="s">
         <v>35</v>
       </c>
-      <c r="K26" s="4" t="s">
+      <c r="K26" s="5" t="s">
         <v>84</v>
       </c>
     </row>
@@ -1976,10 +1983,10 @@
       <c r="D27" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="E27" s="5" t="s">
+      <c r="E27" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="F27" s="5" t="s">
+      <c r="F27" s="6" t="s">
         <v>89</v>
       </c>
       <c r="J27" t="s">
@@ -1999,7 +2006,7 @@
       <c r="D28" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="E28" s="5" t="s">
+      <c r="E28" s="6" t="s">
         <v>90</v>
       </c>
       <c r="J28" t="s">
@@ -2019,7 +2026,7 @@
       <c r="D29" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E29" s="5" t="s">
+      <c r="E29" s="6" t="s">
         <v>91</v>
       </c>
       <c r="J29" t="s">
@@ -2039,13 +2046,13 @@
       <c r="D30" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E30" s="5" t="s">
+      <c r="E30" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="F30" s="5" t="s">
+      <c r="F30" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="G30" s="5" t="s">
+      <c r="G30" s="6" t="s">
         <v>94</v>
       </c>
       <c r="J30" t="s">
@@ -2065,13 +2072,13 @@
       <c r="D31" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="E31" s="5" t="s">
+      <c r="E31" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="F31" s="5" t="s">
+      <c r="F31" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="G31" s="5" t="s">
+      <c r="G31" s="6" t="s">
         <v>97</v>
       </c>
       <c r="J31" t="s">
@@ -2091,10 +2098,10 @@
       <c r="D32" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="E32" s="5" t="s">
+      <c r="E32" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="F32" s="5" t="s">
+      <c r="F32" s="6" t="s">
         <v>99</v>
       </c>
       <c r="J32" t="s">
@@ -2114,10 +2121,10 @@
       <c r="D33" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="E33" s="5" t="s">
+      <c r="E33" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="F33" s="5" t="s">
+      <c r="F33" s="6" t="s">
         <v>101</v>
       </c>
       <c r="J33" t="s">
@@ -2137,10 +2144,10 @@
       <c r="D34" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E34" s="5" t="s">
+      <c r="E34" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="F34" s="5" t="s">
+      <c r="F34" s="6" t="s">
         <v>103</v>
       </c>
       <c r="J34" t="s">
@@ -2160,7 +2167,7 @@
       <c r="D35" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E35" s="5" t="s">
+      <c r="E35" s="6" t="s">
         <v>104</v>
       </c>
       <c r="J35" t="s">
@@ -2180,7 +2187,7 @@
       <c r="D36" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="E36" s="5" t="s">
+      <c r="E36" s="6" t="s">
         <v>105</v>
       </c>
       <c r="J36" t="s">
